--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,479 @@
           <t>Egna observationer</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126049605</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98371</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hällebo-rundan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>513162</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6546739</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126046500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hällebo-rundan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>513162</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6546739</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126046511</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56947</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hällebo-rundan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>513162</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6546739</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126046615</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58366</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hällebo-rundan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>513162</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6546739</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>126049605</v>
       </c>
       <c r="B3" t="n">
-        <v>98371</v>
+        <v>98375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>126049605</v>
       </c>
       <c r="B3" t="n">
-        <v>98375</v>
+        <v>98376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>126049605</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>126046500</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>126046511</v>
       </c>
       <c r="B5" t="n">
-        <v>56947</v>
+        <v>56948</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>126046615</v>
       </c>
       <c r="B6" t="n">
-        <v>58366</v>
+        <v>58367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>126049605</v>
       </c>
       <c r="B3" t="n">
-        <v>98378</v>
+        <v>98380</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,7 +803,7 @@
         <v>126049605</v>
       </c>
       <c r="B3" t="n">
-        <v>98380</v>
+        <v>98382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1271,6 +1271,129 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126293528</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hällebo-rundan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>513162</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6546739</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>126049605</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>98386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>126046500</v>
       </c>
       <c r="B4" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>126046511</v>
       </c>
       <c r="B5" t="n">
-        <v>56948</v>
+        <v>56952</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>126046615</v>
       </c>
       <c r="B6" t="n">
-        <v>58367</v>
+        <v>58371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>126293528</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>57742</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>126049605</v>
       </c>
       <c r="B3" t="n">
-        <v>98386</v>
+        <v>98389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>126049605</v>
       </c>
       <c r="B3" t="n">
-        <v>98389</v>
+        <v>98398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>126046500</v>
       </c>
       <c r="B4" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>126046511</v>
       </c>
       <c r="B5" t="n">
-        <v>56952</v>
+        <v>56953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>126046615</v>
       </c>
       <c r="B6" t="n">
-        <v>58371</v>
+        <v>58374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>126293528</v>
       </c>
       <c r="B7" t="n">
-        <v>57742</v>
+        <v>57743</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,6 +1394,343 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127369105</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103884</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hällebo-rundan, nära gammalt stenröse, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>513101</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6546730</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127369100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100531</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hällebo-rundan, nära gammalt stenröse, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>513101</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6546730</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127368421</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106037</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hällebo-rundan, nära gammalt stenröse, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>513101</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6546730</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre och yngre träd i blandskog av gamla aspar, tall, gran, rönn, lönn och hassel.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>127369105</v>
       </c>
       <c r="B8" t="n">
-        <v>103884</v>
+        <v>103885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127369100</v>
       </c>
       <c r="B9" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>127368421</v>
       </c>
       <c r="B10" t="n">
-        <v>106037</v>
+        <v>106038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>127369105</v>
       </c>
       <c r="B8" t="n">
-        <v>103885</v>
+        <v>103891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127369100</v>
       </c>
       <c r="B9" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>127368421</v>
       </c>
       <c r="B10" t="n">
-        <v>106038</v>
+        <v>106044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>127369105</v>
       </c>
       <c r="B8" t="n">
-        <v>103891</v>
+        <v>103893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127369100</v>
       </c>
       <c r="B9" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>127368421</v>
       </c>
       <c r="B10" t="n">
-        <v>106044</v>
+        <v>106046</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>127369105</v>
       </c>
       <c r="B8" t="n">
-        <v>103893</v>
+        <v>103895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127369100</v>
       </c>
       <c r="B9" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>127368421</v>
       </c>
       <c r="B10" t="n">
-        <v>106046</v>
+        <v>106048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>127369105</v>
       </c>
       <c r="B8" t="n">
-        <v>103895</v>
+        <v>103901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127369100</v>
       </c>
       <c r="B9" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>127368421</v>
       </c>
       <c r="B10" t="n">
-        <v>106048</v>
+        <v>106054</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>127369105</v>
       </c>
       <c r="B8" t="n">
-        <v>103901</v>
+        <v>103904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127369100</v>
       </c>
       <c r="B9" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>127368421</v>
       </c>
       <c r="B10" t="n">
-        <v>106054</v>
+        <v>106057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>127369105</v>
       </c>
       <c r="B8" t="n">
-        <v>103904</v>
+        <v>103912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127369100</v>
       </c>
       <c r="B9" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>127368421</v>
       </c>
       <c r="B10" t="n">
-        <v>106057</v>
+        <v>106065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>127369105</v>
       </c>
       <c r="B8" t="n">
-        <v>103912</v>
+        <v>103913</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127369100</v>
       </c>
       <c r="B9" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>127368421</v>
       </c>
       <c r="B10" t="n">
-        <v>106065</v>
+        <v>106066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>127369105</v>
       </c>
       <c r="B8" t="n">
-        <v>103913</v>
+        <v>103914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127369100</v>
       </c>
       <c r="B9" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>127368421</v>
       </c>
       <c r="B10" t="n">
-        <v>106066</v>
+        <v>106067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -1399,7 +1399,7 @@
         <v>127369105</v>
       </c>
       <c r="B8" t="n">
-        <v>103914</v>
+        <v>103915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127369100</v>
       </c>
       <c r="B9" t="n">
-        <v>100558</v>
+        <v>100559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>127368421</v>
       </c>
       <c r="B10" t="n">
-        <v>106067</v>
+        <v>106068</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>6755449</v>
       </c>
       <c r="B2" t="n">
-        <v>104642</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513282.8215135777</v>
+        <v>513283</v>
       </c>
       <c r="R2" t="n">
-        <v>6546602.590141252</v>
+        <v>6546603</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2003-07-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2003-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126049605</v>
+        <v>126046511</v>
       </c>
       <c r="B3" t="n">
-        <v>98398</v>
+        <v>57247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,31 +796,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -897,7 +886,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,11 +907,11 @@
         <v>126046500</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1035,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126046511</v>
+        <v>126293528</v>
       </c>
       <c r="B5" t="n">
-        <v>56953</v>
+        <v>58039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1069,10 +1057,14 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1112,17 +1104,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1157,7 +1149,7 @@
         <v>126046615</v>
       </c>
       <c r="B6" t="n">
-        <v>58374</v>
+        <v>58676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126293528</v>
+        <v>126049605</v>
       </c>
       <c r="B7" t="n">
-        <v>57743</v>
+        <v>99156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,39 +1276,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102626</v>
+        <v>219875</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1354,17 +1338,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1378,6 +1362,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1396,27 +1381,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127369105</v>
+        <v>127368421</v>
       </c>
       <c r="B8" t="n">
-        <v>103915</v>
+        <v>106813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1424,16 +1409,8 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1476,9 +1453,24 @@
           <t>2025-08-10</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre och yngre träd i blandskog av gamla aspar, tall, gran, rönn, lönn och hassel.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127369100</v>
+        <v>6775262</v>
       </c>
       <c r="B9" t="n">
-        <v>100559</v>
+        <v>106156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,16 +1509,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1536,30 +1528,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällebo-rundan, nära gammalt stenröse, Nrk</t>
+          <t>Källtorp, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513101</v>
+        <v>513293</v>
       </c>
       <c r="R9" t="n">
-        <v>6546730</v>
+        <v>6546612</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,12 +1572,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2004-05-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2004-05-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Test</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,46 +1591,49 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Helena Rygne</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Helena Rygne</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Egna observationer</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127368421</v>
+        <v>134421280</v>
       </c>
       <c r="B10" t="n">
-        <v>106068</v>
+        <v>99960</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>222364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skärmstarr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carex remota</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1644,24 +1641,36 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällebo-rundan, nära gammalt stenröse, Nrk</t>
+          <t>Källtorp, Hjälmsätter, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513101</v>
+        <v>513245</v>
       </c>
       <c r="R10" t="n">
-        <v>6546730</v>
+        <v>6546645</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,27 +1694,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre och yngre träd i blandskog av gamla aspar, tall, gran, rönn, lönn och hassel.</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,15 +1715,235 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Åsa Forsberg, Lena Björk, Helen Lindström, Rolf Wedding, Tomas Gustafson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127369105</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hällebo-rundan, nära gammalt stenröse, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>513101</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6546730</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Helena Johansson</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Helena Johansson</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127369100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hällebo-rundan, nära gammalt stenröse, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>513101</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6546730</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126046615</v>
+        <v>134685616</v>
       </c>
       <c r="B6" t="n">
-        <v>58676</v>
+        <v>58260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,21 +1157,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1179,27 +1179,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällebo-rundan, Nrk</t>
+          <t>Källtorp, Hjälmsätter, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513162</v>
+        <v>513233</v>
       </c>
       <c r="R6" t="n">
-        <v>6546739</v>
+        <v>6546542</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,22 +1231,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Intensivt varnande med föda i näbben. Medobservatör: Markus Herbinger.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,54 +1256,58 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Michael Andersson, Helena Rygne</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126049605</v>
+        <v>126046615</v>
       </c>
       <c r="B7" t="n">
-        <v>99156</v>
+        <v>58676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219875</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1362,7 +1369,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1381,49 +1387,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127368421</v>
+        <v>126049605</v>
       </c>
       <c r="B8" t="n">
-        <v>106813</v>
+        <v>99156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>219875</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällebo-rundan, nära gammalt stenröse, Nrk</t>
+          <t>Hällebo-rundan, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513101</v>
+        <v>513162</v>
       </c>
       <c r="R8" t="n">
-        <v>6546730</v>
+        <v>6546739</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1450,27 +1460,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre och yngre träd i blandskog av gamla aspar, tall, gran, rönn, lönn och hassel.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,27 +1503,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6775262</v>
+        <v>127368421</v>
       </c>
       <c r="B9" t="n">
-        <v>106156</v>
+        <v>106813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1526,29 +1531,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källtorp, Nrk</t>
+          <t>Hällebo-rundan, nära gammalt stenröse, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513293</v>
+        <v>513101</v>
       </c>
       <c r="R9" t="n">
-        <v>6546612</v>
+        <v>6546730</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1572,17 +1572,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2004-05-20</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2004-05-20</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Äldre och yngre träd i blandskog av gamla aspar, tall, gran, rönn, lönn och hassel.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,32 +1601,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helena Rygne</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helena Rygne</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Egna observationer</t>
-        </is>
-      </c>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134421280</v>
+        <v>6775262</v>
       </c>
       <c r="B10" t="n">
-        <v>99960</v>
+        <v>106156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,16 +1631,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222364</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skärmstarr</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carex remota</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1643,34 +1650,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källtorp, Hjälmsätter, Nrk</t>
+          <t>Källtorp, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513245</v>
+        <v>513293</v>
       </c>
       <c r="R10" t="n">
-        <v>6546645</v>
+        <v>6546612</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,12 +1694,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2004-05-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2004-05-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Test</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,29 +1713,32 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Helena Rygne</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michael Andersson, Åsa Forsberg, Lena Björk, Helen Lindström, Rolf Wedding, Tomas Gustafson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Helena Rygne</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Egna observationer</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127369105</v>
+        <v>134421280</v>
       </c>
       <c r="B11" t="n">
-        <v>104628</v>
+        <v>99960</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,16 +1746,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>222364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skärmstarr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Carex remota</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1757,7 +1765,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1767,20 +1775,24 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hällebo-rundan, nära gammalt stenröse, Nrk</t>
+          <t>Källtorp, Hjälmsätter, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513101</v>
+        <v>513245</v>
       </c>
       <c r="R11" t="n">
-        <v>6546730</v>
+        <v>6546645</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,12 +1816,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,22 +1837,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Michael Andersson, Åsa Forsberg, Lena Björk, Helen Lindström, Rolf Wedding, Tomas Gustafson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127369100</v>
+        <v>127369105</v>
       </c>
       <c r="B12" t="n">
-        <v>101228</v>
+        <v>104628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,16 +1860,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1867,7 +1879,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1944,6 +1956,116 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127369100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hällebo-rundan, nära gammalt stenröse, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>513101</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6546730</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -1261,7 +1261,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michael Andersson, Helena Rygne</t>
+          <t>Helena Rygne, Michael Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -1261,7 +1261,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helena Rygne, Michael Andersson</t>
+          <t>Michael Andersson, Helena Rygne</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 10247-2025 artfynd.xlsx
+++ b/artfynd/A 10247-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Egna observationer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6755449</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126046511</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126046500</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,6 +1163,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126293528</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685616</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1384,6 +1414,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126046615</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126049605</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1617,6 +1657,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127368421</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1732,6 +1777,11 @@
           <t>Egna observationer</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6775262</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1846,6 +1896,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134421280</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1956,6 +2011,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127369105</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2066,8 +2126,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127369100</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>